--- a/r5-aist-trustworthyai-poc-pipeline/StructureDefinition-eu-ai-organization.xlsx
+++ b/r5-aist-trustworthyai-poc-pipeline/StructureDefinition-eu-ai-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T09:07:35+00:00</t>
+    <t>2026-06-18T11:52:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>An organization acting as a manufacturer or deployer (owner) of an AI system, containing required regulatory contacts.</t>
+    <t>An Organization profile representing an organization involved in manufacturing, providing, deploying, or operating an AI system, including relevant accountability and contact information.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -4561,7 +4561,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
         <v>260</v>
       </c>
@@ -4580,7 +4580,7 @@
         <v>87</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>88</v>
+        <v>18</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>18</v>
@@ -6665,7 +6665,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
         <v>350</v>
       </c>
@@ -6684,7 +6684,7 @@
         <v>87</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>88</v>
+        <v>18</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>18</v>
